--- a/static/data/exports/Retro_HP_GE_2019.xlsx
+++ b/static/data/exports/Retro_HP_GE_2019.xlsx
@@ -1,13 +1,13 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="Retro Data" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Retro Data" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -577,7 +577,7 @@
         </is>
       </c>
       <c r="Q2" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="R2" t="n">
         <v>37</v>
@@ -2437,7 +2437,7 @@
         </is>
       </c>
       <c r="Q32" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="R32" t="n">
         <v>37</v>
@@ -3181,7 +3181,7 @@
         </is>
       </c>
       <c r="Q44" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="R44" t="n">
         <v>37</v>
@@ -3925,7 +3925,7 @@
         </is>
       </c>
       <c r="Q56" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="R56" t="n">
         <v>37</v>
@@ -4669,7 +4669,7 @@
         </is>
       </c>
       <c r="Q68" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="R68" t="n">
         <v>37</v>
@@ -5413,7 +5413,7 @@
         </is>
       </c>
       <c r="Q80" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="R80" t="n">
         <v>37</v>
@@ -6157,7 +6157,7 @@
         </is>
       </c>
       <c r="Q92" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="R92" t="n">
         <v>37</v>
@@ -6901,7 +6901,7 @@
         </is>
       </c>
       <c r="Q104" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="R104" t="n">
         <v>37</v>
@@ -9133,7 +9133,7 @@
         </is>
       </c>
       <c r="Q140" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="R140" t="n">
         <v>37</v>
@@ -9877,7 +9877,7 @@
         </is>
       </c>
       <c r="Q152" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="R152" t="n">
         <v>37</v>
@@ -10621,7 +10621,7 @@
         </is>
       </c>
       <c r="Q164" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="R164" t="n">
         <v>37</v>
@@ -11365,7 +11365,7 @@
         </is>
       </c>
       <c r="Q176" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="R176" t="n">
         <v>37</v>
@@ -12109,7 +12109,7 @@
         </is>
       </c>
       <c r="Q188" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="R188" t="n">
         <v>37</v>
@@ -12853,7 +12853,7 @@
         </is>
       </c>
       <c r="Q200" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="R200" t="n">
         <v>37</v>
@@ -13597,7 +13597,7 @@
         </is>
       </c>
       <c r="Q212" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="R212" t="n">
         <v>37</v>
@@ -14341,7 +14341,7 @@
         </is>
       </c>
       <c r="Q224" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="R224" t="n">
         <v>37</v>
@@ -15085,7 +15085,7 @@
         </is>
       </c>
       <c r="Q236" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="R236" t="n">
         <v>37</v>
@@ -16775,20 +16775,20 @@
     </row>
     <row r="264">
       <c r="A264" t="n">
-        <v>1507285</v>
+        <v>1507284</v>
       </c>
       <c r="B264" t="inlineStr">
         <is>
-          <t>KHEM CHAND</t>
+          <t>CHANDERMANI</t>
         </is>
       </c>
       <c r="C264" t="inlineStr">
         <is>
-          <t>PPID</t>
+          <t>AIFB</t>
         </is>
       </c>
       <c r="D264" t="n">
-        <v>16556</v>
+        <v>16557</v>
       </c>
       <c r="E264" t="n">
         <v>6</v>
@@ -16812,12 +16812,12 @@
       </c>
       <c r="K264" t="inlineStr">
         <is>
-          <t>KHEM CHAND</t>
+          <t>CHANDERMANI</t>
         </is>
       </c>
       <c r="L264" t="inlineStr">
         <is>
-          <t>PPID</t>
+          <t>AIFB</t>
         </is>
       </c>
       <c r="Q264" t="b">
@@ -16837,20 +16837,20 @@
     </row>
     <row r="265">
       <c r="A265" t="n">
-        <v>1507284</v>
+        <v>1507285</v>
       </c>
       <c r="B265" t="inlineStr">
         <is>
-          <t>CHANDERMANI</t>
+          <t>KHEM CHAND</t>
         </is>
       </c>
       <c r="C265" t="inlineStr">
         <is>
-          <t>AIFB</t>
+          <t>PPID</t>
         </is>
       </c>
       <c r="D265" t="n">
-        <v>16557</v>
+        <v>16556</v>
       </c>
       <c r="E265" t="n">
         <v>6</v>
@@ -16874,12 +16874,12 @@
       </c>
       <c r="K265" t="inlineStr">
         <is>
-          <t>CHANDERMANI</t>
+          <t>KHEM CHAND</t>
         </is>
       </c>
       <c r="L265" t="inlineStr">
         <is>
-          <t>AIFB</t>
+          <t>PPID</t>
         </is>
       </c>
       <c r="Q265" t="b">
@@ -25393,20 +25393,20 @@
     </row>
     <row r="403">
       <c r="A403" t="n">
-        <v>1507776</v>
+        <v>1507777</v>
       </c>
       <c r="B403" t="inlineStr">
         <is>
-          <t>GHANSHYAM CHAND THAKUR</t>
+          <t>KARTAR CHAND</t>
         </is>
       </c>
       <c r="C403" t="inlineStr">
         <is>
-          <t>IND</t>
+          <t>SWAP</t>
         </is>
       </c>
       <c r="D403" t="n">
-        <v>16536</v>
+        <v>16547</v>
       </c>
       <c r="E403" t="n">
         <v>51</v>
@@ -25430,12 +25430,12 @@
       </c>
       <c r="K403" t="inlineStr">
         <is>
-          <t>GHANSHYAM CHAND THAKUR</t>
+          <t>KARTAR CHAND</t>
         </is>
       </c>
       <c r="L403" t="inlineStr">
         <is>
-          <t>IND</t>
+          <t>SWAP</t>
         </is>
       </c>
       <c r="Q403" t="b">
@@ -25455,20 +25455,20 @@
     </row>
     <row r="404">
       <c r="A404" t="n">
-        <v>1507777</v>
+        <v>1507776</v>
       </c>
       <c r="B404" t="inlineStr">
         <is>
-          <t>KARTAR CHAND</t>
+          <t>GHANSHYAM CHAND THAKUR</t>
         </is>
       </c>
       <c r="C404" t="inlineStr">
         <is>
-          <t>SWAP</t>
+          <t>IND</t>
         </is>
       </c>
       <c r="D404" t="n">
-        <v>16547</v>
+        <v>16536</v>
       </c>
       <c r="E404" t="n">
         <v>51</v>
@@ -25492,12 +25492,12 @@
       </c>
       <c r="K404" t="inlineStr">
         <is>
-          <t>KARTAR CHAND</t>
+          <t>GHANSHYAM CHAND THAKUR</t>
         </is>
       </c>
       <c r="L404" t="inlineStr">
         <is>
-          <t>SWAP</t>
+          <t>IND</t>
         </is>
       </c>
       <c r="Q404" t="b">
@@ -26571,20 +26571,20 @@
     </row>
     <row r="422">
       <c r="A422" t="n">
-        <v>1507838</v>
+        <v>1507839</v>
       </c>
       <c r="B422" t="inlineStr">
         <is>
-          <t>KARTAR CHAND</t>
+          <t>KHEM CHAND</t>
         </is>
       </c>
       <c r="C422" t="inlineStr">
         <is>
-          <t>SWAP</t>
+          <t>PPID</t>
         </is>
       </c>
       <c r="D422" t="n">
-        <v>16547</v>
+        <v>16556</v>
       </c>
       <c r="E422" t="n">
         <v>60</v>
@@ -26608,12 +26608,12 @@
       </c>
       <c r="K422" t="inlineStr">
         <is>
-          <t>KARTAR CHAND</t>
+          <t>KHEM CHAND</t>
         </is>
       </c>
       <c r="L422" t="inlineStr">
         <is>
-          <t>SWAP</t>
+          <t>PPID</t>
         </is>
       </c>
       <c r="Q422" t="b">
@@ -26633,20 +26633,20 @@
     </row>
     <row r="423">
       <c r="A423" t="n">
-        <v>1507839</v>
+        <v>1507838</v>
       </c>
       <c r="B423" t="inlineStr">
         <is>
-          <t>KHEM CHAND</t>
+          <t>KARTAR CHAND</t>
         </is>
       </c>
       <c r="C423" t="inlineStr">
         <is>
-          <t>PPID</t>
+          <t>SWAP</t>
         </is>
       </c>
       <c r="D423" t="n">
-        <v>16556</v>
+        <v>16547</v>
       </c>
       <c r="E423" t="n">
         <v>60</v>
@@ -26670,12 +26670,12 @@
       </c>
       <c r="K423" t="inlineStr">
         <is>
-          <t>KHEM CHAND</t>
+          <t>KARTAR CHAND</t>
         </is>
       </c>
       <c r="L423" t="inlineStr">
         <is>
-          <t>PPID</t>
+          <t>SWAP</t>
         </is>
       </c>
       <c r="Q423" t="b">
@@ -28493,20 +28493,20 @@
     </row>
     <row r="453">
       <c r="A453" t="n">
-        <v>1507966</v>
+        <v>1507965</v>
       </c>
       <c r="B453" t="inlineStr">
         <is>
-          <t>TULSI RAM SHARMA</t>
+          <t>PARVEEN THAKUR</t>
         </is>
       </c>
       <c r="C453" t="inlineStr">
         <is>
-          <t>AIFB</t>
+          <t>IND</t>
         </is>
       </c>
       <c r="D453" t="n">
-        <v>16557</v>
+        <v>16536</v>
       </c>
       <c r="E453" t="n">
         <v>34</v>
@@ -28530,12 +28530,12 @@
       </c>
       <c r="K453" t="inlineStr">
         <is>
-          <t>TULSI RAM SHARMA</t>
+          <t>PARVEEN THAKUR</t>
         </is>
       </c>
       <c r="L453" t="inlineStr">
         <is>
-          <t>AIFB</t>
+          <t>IND</t>
         </is>
       </c>
       <c r="Q453" t="b">
@@ -28555,20 +28555,20 @@
     </row>
     <row r="454">
       <c r="A454" t="n">
-        <v>1507965</v>
+        <v>1507966</v>
       </c>
       <c r="B454" t="inlineStr">
         <is>
-          <t>PARVEEN THAKUR</t>
+          <t>TULSI RAM SHARMA</t>
         </is>
       </c>
       <c r="C454" t="inlineStr">
         <is>
-          <t>IND</t>
+          <t>AIFB</t>
         </is>
       </c>
       <c r="D454" t="n">
-        <v>16536</v>
+        <v>16557</v>
       </c>
       <c r="E454" t="n">
         <v>34</v>
@@ -28592,12 +28592,12 @@
       </c>
       <c r="K454" t="inlineStr">
         <is>
-          <t>PARVEEN THAKUR</t>
+          <t>TULSI RAM SHARMA</t>
         </is>
       </c>
       <c r="L454" t="inlineStr">
         <is>
-          <t>IND</t>
+          <t>AIFB</t>
         </is>
       </c>
       <c r="Q454" t="b">
@@ -31779,20 +31779,20 @@
     </row>
     <row r="506">
       <c r="A506" t="n">
-        <v>1508160</v>
+        <v>1508161</v>
       </c>
       <c r="B506" t="inlineStr">
         <is>
-          <t>CHANDERMANI</t>
+          <t>GHANSHYAM CHAND THAKUR</t>
         </is>
       </c>
       <c r="C506" t="inlineStr">
         <is>
-          <t>AIFB</t>
+          <t>IND</t>
         </is>
       </c>
       <c r="D506" t="n">
-        <v>16557</v>
+        <v>16536</v>
       </c>
       <c r="E506" t="n">
         <v>36</v>
@@ -31816,12 +31816,12 @@
       </c>
       <c r="K506" t="inlineStr">
         <is>
-          <t>CHANDERMANI</t>
+          <t>GHANSHYAM CHAND THAKUR</t>
         </is>
       </c>
       <c r="L506" t="inlineStr">
         <is>
-          <t>AIFB</t>
+          <t>IND</t>
         </is>
       </c>
       <c r="Q506" t="b">
@@ -31841,20 +31841,20 @@
     </row>
     <row r="507">
       <c r="A507" t="n">
-        <v>1508161</v>
+        <v>1508160</v>
       </c>
       <c r="B507" t="inlineStr">
         <is>
-          <t>GHANSHYAM CHAND THAKUR</t>
+          <t>CHANDERMANI</t>
         </is>
       </c>
       <c r="C507" t="inlineStr">
         <is>
-          <t>IND</t>
+          <t>AIFB</t>
         </is>
       </c>
       <c r="D507" t="n">
-        <v>16536</v>
+        <v>16557</v>
       </c>
       <c r="E507" t="n">
         <v>36</v>
@@ -31878,12 +31878,12 @@
       </c>
       <c r="K507" t="inlineStr">
         <is>
-          <t>GHANSHYAM CHAND THAKUR</t>
+          <t>CHANDERMANI</t>
         </is>
       </c>
       <c r="L507" t="inlineStr">
         <is>
-          <t>IND</t>
+          <t>AIFB</t>
         </is>
       </c>
       <c r="Q507" t="b">
@@ -34011,20 +34011,20 @@
     </row>
     <row r="542">
       <c r="A542" t="n">
-        <v>1508345</v>
+        <v>1508346</v>
       </c>
       <c r="B542" t="inlineStr">
         <is>
-          <t>RAM SINGH SHUKLA</t>
+          <t>VIKASH KUMAR</t>
         </is>
       </c>
       <c r="C542" t="inlineStr">
         <is>
-          <t>BMUP</t>
+          <t>IND</t>
         </is>
       </c>
       <c r="D542" t="n">
-        <v>16544</v>
+        <v>16536</v>
       </c>
       <c r="E542" t="n">
         <v>52</v>
@@ -34048,12 +34048,12 @@
       </c>
       <c r="K542" t="inlineStr">
         <is>
-          <t>RAM SINGH SHUKLA</t>
+          <t>VIKASH KUMAR</t>
         </is>
       </c>
       <c r="L542" t="inlineStr">
         <is>
-          <t>BMUP</t>
+          <t>IND</t>
         </is>
       </c>
       <c r="Q542" t="b">
@@ -34073,20 +34073,20 @@
     </row>
     <row r="543">
       <c r="A543" t="n">
-        <v>1508346</v>
+        <v>1508345</v>
       </c>
       <c r="B543" t="inlineStr">
         <is>
-          <t>VIKASH KUMAR</t>
+          <t>RAM SINGH SHUKLA</t>
         </is>
       </c>
       <c r="C543" t="inlineStr">
         <is>
-          <t>IND</t>
+          <t>BMUP</t>
         </is>
       </c>
       <c r="D543" t="n">
-        <v>16536</v>
+        <v>16544</v>
       </c>
       <c r="E543" t="n">
         <v>52</v>
@@ -34110,12 +34110,12 @@
       </c>
       <c r="K543" t="inlineStr">
         <is>
-          <t>VIKASH KUMAR</t>
+          <t>RAM SINGH SHUKLA</t>
         </is>
       </c>
       <c r="L543" t="inlineStr">
         <is>
-          <t>IND</t>
+          <t>BMUP</t>
         </is>
       </c>
       <c r="Q543" t="b">
@@ -36925,11 +36925,11 @@
     </row>
     <row r="589">
       <c r="A589" t="n">
-        <v>1508577</v>
+        <v>1508576</v>
       </c>
       <c r="B589" t="inlineStr">
         <is>
-          <t>VIKASH KUMAR</t>
+          <t>RADHA KRISHAN NAROTRA</t>
         </is>
       </c>
       <c r="C589" t="inlineStr">
@@ -36962,7 +36962,7 @@
       </c>
       <c r="K589" t="inlineStr">
         <is>
-          <t>VIKASH KUMAR</t>
+          <t>RADHA KRISHAN NAROTRA</t>
         </is>
       </c>
       <c r="L589" t="inlineStr">
@@ -36987,11 +36987,11 @@
     </row>
     <row r="590">
       <c r="A590" t="n">
-        <v>1508576</v>
+        <v>1508577</v>
       </c>
       <c r="B590" t="inlineStr">
         <is>
-          <t>RADHA KRISHAN NAROTRA</t>
+          <t>VIKASH KUMAR</t>
         </is>
       </c>
       <c r="C590" t="inlineStr">
@@ -37024,7 +37024,7 @@
       </c>
       <c r="K590" t="inlineStr">
         <is>
-          <t>RADHA KRISHAN NAROTRA</t>
+          <t>VIKASH KUMAR</t>
         </is>
       </c>
       <c r="L590" t="inlineStr">
@@ -42613,7 +42613,7 @@
         </is>
       </c>
       <c r="Q680" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="R680" t="n">
         <v>37</v>
@@ -43047,7 +43047,7 @@
         </is>
       </c>
       <c r="Q687" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="R687" t="n">
         <v>37</v>
@@ -43481,7 +43481,7 @@
         </is>
       </c>
       <c r="Q694" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="R694" t="n">
         <v>37</v>
@@ -43915,7 +43915,7 @@
         </is>
       </c>
       <c r="Q701" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="R701" t="n">
         <v>37</v>
@@ -44349,7 +44349,7 @@
         </is>
       </c>
       <c r="Q708" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="R708" t="n">
         <v>37</v>
@@ -44783,7 +44783,7 @@
         </is>
       </c>
       <c r="Q715" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="R715" t="n">
         <v>37</v>
@@ -45217,7 +45217,7 @@
         </is>
       </c>
       <c r="Q722" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="R722" t="n">
         <v>37</v>
@@ -45651,7 +45651,7 @@
         </is>
       </c>
       <c r="Q729" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="R729" t="n">
         <v>37</v>
@@ -46085,7 +46085,7 @@
         </is>
       </c>
       <c r="Q736" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="R736" t="n">
         <v>37</v>
@@ -46519,7 +46519,7 @@
         </is>
       </c>
       <c r="Q743" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="R743" t="n">
         <v>37</v>
@@ -46953,7 +46953,7 @@
         </is>
       </c>
       <c r="Q750" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="R750" t="n">
         <v>37</v>
@@ -47387,7 +47387,7 @@
         </is>
       </c>
       <c r="Q757" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="R757" t="n">
         <v>37</v>
@@ -47821,7 +47821,7 @@
         </is>
       </c>
       <c r="Q764" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="R764" t="n">
         <v>37</v>
@@ -48255,7 +48255,7 @@
         </is>
       </c>
       <c r="Q771" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="R771" t="n">
         <v>37</v>
@@ -48689,7 +48689,7 @@
         </is>
       </c>
       <c r="Q778" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="R778" t="n">
         <v>37</v>
@@ -49123,7 +49123,7 @@
         </is>
       </c>
       <c r="Q785" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="R785" t="n">
         <v>37</v>
@@ -50673,7 +50673,7 @@
         </is>
       </c>
       <c r="Q810" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="R810" t="n">
         <v>37</v>

--- a/static/data/exports/Retro_HP_GE_2019.xlsx
+++ b/static/data/exports/Retro_HP_GE_2019.xlsx
@@ -1408,11 +1408,11 @@
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>CPM</t>
+          <t>CPI(M)</t>
         </is>
       </c>
       <c r="D16" t="n">
-        <v>16552</v>
+        <v>26432</v>
       </c>
       <c r="E16" t="n">
         <v>520</v>
@@ -7847,20 +7847,20 @@
     </row>
     <row r="120">
       <c r="A120" t="n">
-        <v>1506585</v>
+        <v>1506584</v>
       </c>
       <c r="B120" t="inlineStr">
         <is>
-          <t>RADHA KRISHAN NAROTRA</t>
+          <t>KRISHAN GOPAL</t>
         </is>
       </c>
       <c r="C120" t="inlineStr">
         <is>
-          <t>IND</t>
+          <t>SatBP</t>
         </is>
       </c>
       <c r="D120" t="n">
-        <v>16536</v>
+        <v>16565</v>
       </c>
       <c r="E120" t="n">
         <v>103</v>
@@ -7884,12 +7884,12 @@
       </c>
       <c r="K120" t="inlineStr">
         <is>
-          <t>RADHA KRISHAN NAROTRA</t>
+          <t>KRISHAN GOPAL</t>
         </is>
       </c>
       <c r="L120" t="inlineStr">
         <is>
-          <t>IND</t>
+          <t>SatBP</t>
         </is>
       </c>
       <c r="Q120" t="b">
@@ -7909,20 +7909,20 @@
     </row>
     <row r="121">
       <c r="A121" t="n">
-        <v>1506584</v>
+        <v>1506585</v>
       </c>
       <c r="B121" t="inlineStr">
         <is>
-          <t>KRISHAN GOPAL</t>
+          <t>RADHA KRISHAN NAROTRA</t>
         </is>
       </c>
       <c r="C121" t="inlineStr">
         <is>
-          <t>SatBP</t>
+          <t>IND</t>
         </is>
       </c>
       <c r="D121" t="n">
-        <v>16565</v>
+        <v>16536</v>
       </c>
       <c r="E121" t="n">
         <v>103</v>
@@ -7946,12 +7946,12 @@
       </c>
       <c r="K121" t="inlineStr">
         <is>
-          <t>KRISHAN GOPAL</t>
+          <t>RADHA KRISHAN NAROTRA</t>
         </is>
       </c>
       <c r="L121" t="inlineStr">
         <is>
-          <t>SatBP</t>
+          <t>IND</t>
         </is>
       </c>
       <c r="Q121" t="b">
@@ -8963,20 +8963,20 @@
     </row>
     <row r="138">
       <c r="A138" t="n">
-        <v>1506658</v>
+        <v>1506657</v>
       </c>
       <c r="B138" t="inlineStr">
         <is>
-          <t>TULSI RAM SHARMA</t>
+          <t>ASHOK SHARMA</t>
         </is>
       </c>
       <c r="C138" t="inlineStr">
         <is>
-          <t>AIFB</t>
+          <t>IND</t>
         </is>
       </c>
       <c r="D138" t="n">
-        <v>16557</v>
+        <v>16536</v>
       </c>
       <c r="E138" t="n">
         <v>14</v>
@@ -9000,12 +9000,12 @@
       </c>
       <c r="K138" t="inlineStr">
         <is>
-          <t>TULSI RAM SHARMA</t>
+          <t>ASHOK SHARMA</t>
         </is>
       </c>
       <c r="L138" t="inlineStr">
         <is>
-          <t>AIFB</t>
+          <t>IND</t>
         </is>
       </c>
       <c r="Q138" t="b">
@@ -9025,20 +9025,20 @@
     </row>
     <row r="139">
       <c r="A139" t="n">
-        <v>1506657</v>
+        <v>1506658</v>
       </c>
       <c r="B139" t="inlineStr">
         <is>
-          <t>ASHOK SHARMA</t>
+          <t>TULSI RAM SHARMA</t>
         </is>
       </c>
       <c r="C139" t="inlineStr">
         <is>
-          <t>IND</t>
+          <t>AIFB</t>
         </is>
       </c>
       <c r="D139" t="n">
-        <v>16536</v>
+        <v>16557</v>
       </c>
       <c r="E139" t="n">
         <v>14</v>
@@ -9062,12 +9062,12 @@
       </c>
       <c r="K139" t="inlineStr">
         <is>
-          <t>ASHOK SHARMA</t>
+          <t>TULSI RAM SHARMA</t>
         </is>
       </c>
       <c r="L139" t="inlineStr">
         <is>
-          <t>IND</t>
+          <t>AIFB</t>
         </is>
       </c>
       <c r="Q139" t="b">
@@ -15916,11 +15916,11 @@
       </c>
       <c r="C250" t="inlineStr">
         <is>
-          <t>CPM</t>
+          <t>CPI(M)</t>
         </is>
       </c>
       <c r="D250" t="n">
-        <v>16552</v>
+        <v>26432</v>
       </c>
       <c r="E250" t="n">
         <v>137</v>
@@ -16775,20 +16775,20 @@
     </row>
     <row r="264">
       <c r="A264" t="n">
-        <v>1507284</v>
+        <v>1507285</v>
       </c>
       <c r="B264" t="inlineStr">
         <is>
-          <t>CHANDERMANI</t>
+          <t>KHEM CHAND</t>
         </is>
       </c>
       <c r="C264" t="inlineStr">
         <is>
-          <t>AIFB</t>
+          <t>PPID</t>
         </is>
       </c>
       <c r="D264" t="n">
-        <v>16557</v>
+        <v>16556</v>
       </c>
       <c r="E264" t="n">
         <v>6</v>
@@ -16812,12 +16812,12 @@
       </c>
       <c r="K264" t="inlineStr">
         <is>
-          <t>CHANDERMANI</t>
+          <t>KHEM CHAND</t>
         </is>
       </c>
       <c r="L264" t="inlineStr">
         <is>
-          <t>AIFB</t>
+          <t>PPID</t>
         </is>
       </c>
       <c r="Q264" t="b">
@@ -16837,20 +16837,20 @@
     </row>
     <row r="265">
       <c r="A265" t="n">
-        <v>1507285</v>
+        <v>1507284</v>
       </c>
       <c r="B265" t="inlineStr">
         <is>
-          <t>KHEM CHAND</t>
+          <t>CHANDERMANI</t>
         </is>
       </c>
       <c r="C265" t="inlineStr">
         <is>
-          <t>PPID</t>
+          <t>AIFB</t>
         </is>
       </c>
       <c r="D265" t="n">
-        <v>16556</v>
+        <v>16557</v>
       </c>
       <c r="E265" t="n">
         <v>6</v>
@@ -16874,12 +16874,12 @@
       </c>
       <c r="K265" t="inlineStr">
         <is>
-          <t>KHEM CHAND</t>
+          <t>CHANDERMANI</t>
         </is>
       </c>
       <c r="L265" t="inlineStr">
         <is>
-          <t>PPID</t>
+          <t>AIFB</t>
         </is>
       </c>
       <c r="Q265" t="b">
@@ -17094,11 +17094,11 @@
       </c>
       <c r="C269" t="inlineStr">
         <is>
-          <t>CPM</t>
+          <t>CPI(M)</t>
         </is>
       </c>
       <c r="D269" t="n">
-        <v>16552</v>
+        <v>26432</v>
       </c>
       <c r="E269" t="n">
         <v>588</v>
@@ -18148,11 +18148,11 @@
       </c>
       <c r="C286" t="inlineStr">
         <is>
-          <t>CPM</t>
+          <t>CPI(M)</t>
         </is>
       </c>
       <c r="D286" t="n">
-        <v>16552</v>
+        <v>26432</v>
       </c>
       <c r="E286" t="n">
         <v>1120</v>
@@ -19326,11 +19326,11 @@
       </c>
       <c r="C305" t="inlineStr">
         <is>
-          <t>CPM</t>
+          <t>CPI(M)</t>
         </is>
       </c>
       <c r="D305" t="n">
-        <v>16552</v>
+        <v>26432</v>
       </c>
       <c r="E305" t="n">
         <v>635</v>
@@ -20380,11 +20380,11 @@
       </c>
       <c r="C322" t="inlineStr">
         <is>
-          <t>CPM</t>
+          <t>CPI(M)</t>
         </is>
       </c>
       <c r="D322" t="n">
-        <v>16552</v>
+        <v>26432</v>
       </c>
       <c r="E322" t="n">
         <v>2134</v>
@@ -21496,11 +21496,11 @@
       </c>
       <c r="C340" t="inlineStr">
         <is>
-          <t>CPM</t>
+          <t>CPI(M)</t>
         </is>
       </c>
       <c r="D340" t="n">
-        <v>16552</v>
+        <v>26432</v>
       </c>
       <c r="E340" t="n">
         <v>645</v>
@@ -22674,11 +22674,11 @@
       </c>
       <c r="C359" t="inlineStr">
         <is>
-          <t>CPM</t>
+          <t>CPI(M)</t>
         </is>
       </c>
       <c r="D359" t="n">
-        <v>16552</v>
+        <v>26432</v>
       </c>
       <c r="E359" t="n">
         <v>394</v>
@@ -23409,20 +23409,20 @@
     </row>
     <row r="371">
       <c r="A371" t="n">
-        <v>1507659</v>
+        <v>1507660</v>
       </c>
       <c r="B371" t="inlineStr">
         <is>
-          <t>CHANDERMANI</t>
+          <t>MEHAR SINGH</t>
         </is>
       </c>
       <c r="C371" t="inlineStr">
         <is>
-          <t>AIFB</t>
+          <t>RADM</t>
         </is>
       </c>
       <c r="D371" t="n">
-        <v>16557</v>
+        <v>16555</v>
       </c>
       <c r="E371" t="n">
         <v>24</v>
@@ -23446,12 +23446,12 @@
       </c>
       <c r="K371" t="inlineStr">
         <is>
-          <t>CHANDERMANI</t>
+          <t>MEHAR SINGH</t>
         </is>
       </c>
       <c r="L371" t="inlineStr">
         <is>
-          <t>AIFB</t>
+          <t>RADM</t>
         </is>
       </c>
       <c r="Q371" t="b">
@@ -23471,20 +23471,20 @@
     </row>
     <row r="372">
       <c r="A372" t="n">
-        <v>1507660</v>
+        <v>1507659</v>
       </c>
       <c r="B372" t="inlineStr">
         <is>
-          <t>MEHAR SINGH</t>
+          <t>CHANDERMANI</t>
         </is>
       </c>
       <c r="C372" t="inlineStr">
         <is>
-          <t>RADM</t>
+          <t>AIFB</t>
         </is>
       </c>
       <c r="D372" t="n">
-        <v>16555</v>
+        <v>16557</v>
       </c>
       <c r="E372" t="n">
         <v>24</v>
@@ -23508,12 +23508,12 @@
       </c>
       <c r="K372" t="inlineStr">
         <is>
-          <t>MEHAR SINGH</t>
+          <t>CHANDERMANI</t>
         </is>
       </c>
       <c r="L372" t="inlineStr">
         <is>
-          <t>RADM</t>
+          <t>AIFB</t>
         </is>
       </c>
       <c r="Q372" t="b">
@@ -23790,11 +23790,11 @@
       </c>
       <c r="C377" t="inlineStr">
         <is>
-          <t>CPM</t>
+          <t>CPI(M)</t>
         </is>
       </c>
       <c r="D377" t="n">
-        <v>16552</v>
+        <v>26432</v>
       </c>
       <c r="E377" t="n">
         <v>459</v>
@@ -24844,11 +24844,11 @@
       </c>
       <c r="C394" t="inlineStr">
         <is>
-          <t>CPM</t>
+          <t>CPI(M)</t>
         </is>
       </c>
       <c r="D394" t="n">
-        <v>16552</v>
+        <v>26432</v>
       </c>
       <c r="E394" t="n">
         <v>732</v>
@@ -25393,20 +25393,20 @@
     </row>
     <row r="403">
       <c r="A403" t="n">
-        <v>1507777</v>
+        <v>1507776</v>
       </c>
       <c r="B403" t="inlineStr">
         <is>
-          <t>KARTAR CHAND</t>
+          <t>GHANSHYAM CHAND THAKUR</t>
         </is>
       </c>
       <c r="C403" t="inlineStr">
         <is>
-          <t>SWAP</t>
+          <t>IND</t>
         </is>
       </c>
       <c r="D403" t="n">
-        <v>16547</v>
+        <v>16536</v>
       </c>
       <c r="E403" t="n">
         <v>51</v>
@@ -25430,12 +25430,12 @@
       </c>
       <c r="K403" t="inlineStr">
         <is>
-          <t>KARTAR CHAND</t>
+          <t>GHANSHYAM CHAND THAKUR</t>
         </is>
       </c>
       <c r="L403" t="inlineStr">
         <is>
-          <t>SWAP</t>
+          <t>IND</t>
         </is>
       </c>
       <c r="Q403" t="b">
@@ -25455,20 +25455,20 @@
     </row>
     <row r="404">
       <c r="A404" t="n">
-        <v>1507776</v>
+        <v>1507777</v>
       </c>
       <c r="B404" t="inlineStr">
         <is>
-          <t>GHANSHYAM CHAND THAKUR</t>
+          <t>KARTAR CHAND</t>
         </is>
       </c>
       <c r="C404" t="inlineStr">
         <is>
-          <t>IND</t>
+          <t>SWAP</t>
         </is>
       </c>
       <c r="D404" t="n">
-        <v>16536</v>
+        <v>16547</v>
       </c>
       <c r="E404" t="n">
         <v>51</v>
@@ -25492,12 +25492,12 @@
       </c>
       <c r="K404" t="inlineStr">
         <is>
-          <t>GHANSHYAM CHAND THAKUR</t>
+          <t>KARTAR CHAND</t>
         </is>
       </c>
       <c r="L404" t="inlineStr">
         <is>
-          <t>IND</t>
+          <t>SWAP</t>
         </is>
       </c>
       <c r="Q404" t="b">
@@ -25960,11 +25960,11 @@
       </c>
       <c r="C412" t="inlineStr">
         <is>
-          <t>CPM</t>
+          <t>CPI(M)</t>
         </is>
       </c>
       <c r="D412" t="n">
-        <v>16552</v>
+        <v>26432</v>
       </c>
       <c r="E412" t="n">
         <v>509</v>
@@ -27076,11 +27076,11 @@
       </c>
       <c r="C430" t="inlineStr">
         <is>
-          <t>CPM</t>
+          <t>CPI(M)</t>
         </is>
       </c>
       <c r="D430" t="n">
-        <v>16552</v>
+        <v>26432</v>
       </c>
       <c r="E430" t="n">
         <v>1553</v>
@@ -28998,11 +28998,11 @@
       </c>
       <c r="C461" t="inlineStr">
         <is>
-          <t>CPM</t>
+          <t>CPI(M)</t>
         </is>
       </c>
       <c r="D461" t="n">
-        <v>16552</v>
+        <v>26432</v>
       </c>
       <c r="E461" t="n">
         <v>391</v>
@@ -30114,11 +30114,11 @@
       </c>
       <c r="C479" t="inlineStr">
         <is>
-          <t>CPM</t>
+          <t>CPI(M)</t>
         </is>
       </c>
       <c r="D479" t="n">
-        <v>16552</v>
+        <v>26432</v>
       </c>
       <c r="E479" t="n">
         <v>383</v>
@@ -31168,11 +31168,11 @@
       </c>
       <c r="C496" t="inlineStr">
         <is>
-          <t>CPM</t>
+          <t>CPI(M)</t>
         </is>
       </c>
       <c r="D496" t="n">
-        <v>16552</v>
+        <v>26432</v>
       </c>
       <c r="E496" t="n">
         <v>659</v>
@@ -31779,20 +31779,20 @@
     </row>
     <row r="506">
       <c r="A506" t="n">
-        <v>1508161</v>
+        <v>1508160</v>
       </c>
       <c r="B506" t="inlineStr">
         <is>
-          <t>GHANSHYAM CHAND THAKUR</t>
+          <t>CHANDERMANI</t>
         </is>
       </c>
       <c r="C506" t="inlineStr">
         <is>
-          <t>IND</t>
+          <t>AIFB</t>
         </is>
       </c>
       <c r="D506" t="n">
-        <v>16536</v>
+        <v>16557</v>
       </c>
       <c r="E506" t="n">
         <v>36</v>
@@ -31816,12 +31816,12 @@
       </c>
       <c r="K506" t="inlineStr">
         <is>
-          <t>GHANSHYAM CHAND THAKUR</t>
+          <t>CHANDERMANI</t>
         </is>
       </c>
       <c r="L506" t="inlineStr">
         <is>
-          <t>IND</t>
+          <t>AIFB</t>
         </is>
       </c>
       <c r="Q506" t="b">
@@ -31841,20 +31841,20 @@
     </row>
     <row r="507">
       <c r="A507" t="n">
-        <v>1508160</v>
+        <v>1508161</v>
       </c>
       <c r="B507" t="inlineStr">
         <is>
-          <t>CHANDERMANI</t>
+          <t>GHANSHYAM CHAND THAKUR</t>
         </is>
       </c>
       <c r="C507" t="inlineStr">
         <is>
-          <t>AIFB</t>
+          <t>IND</t>
         </is>
       </c>
       <c r="D507" t="n">
-        <v>16557</v>
+        <v>16536</v>
       </c>
       <c r="E507" t="n">
         <v>36</v>
@@ -31878,12 +31878,12 @@
       </c>
       <c r="K507" t="inlineStr">
         <is>
-          <t>CHANDERMANI</t>
+          <t>GHANSHYAM CHAND THAKUR</t>
         </is>
       </c>
       <c r="L507" t="inlineStr">
         <is>
-          <t>AIFB</t>
+          <t>IND</t>
         </is>
       </c>
       <c r="Q507" t="b">
@@ -35685,20 +35685,20 @@
     </row>
     <row r="569">
       <c r="A569" t="n">
-        <v>1508473</v>
+        <v>1508472</v>
       </c>
       <c r="B569" t="inlineStr">
         <is>
-          <t>RAM SINGH SHUKLA</t>
+          <t>ASHOK SHARMA</t>
         </is>
       </c>
       <c r="C569" t="inlineStr">
         <is>
-          <t>BMUP</t>
+          <t>IND</t>
         </is>
       </c>
       <c r="D569" t="n">
-        <v>16544</v>
+        <v>16536</v>
       </c>
       <c r="E569" t="n">
         <v>18</v>
@@ -35722,12 +35722,12 @@
       </c>
       <c r="K569" t="inlineStr">
         <is>
-          <t>RAM SINGH SHUKLA</t>
+          <t>ASHOK SHARMA</t>
         </is>
       </c>
       <c r="L569" t="inlineStr">
         <is>
-          <t>BMUP</t>
+          <t>IND</t>
         </is>
       </c>
       <c r="Q569" t="b">
@@ -35747,20 +35747,20 @@
     </row>
     <row r="570">
       <c r="A570" t="n">
-        <v>1508472</v>
+        <v>1508473</v>
       </c>
       <c r="B570" t="inlineStr">
         <is>
-          <t>ASHOK SHARMA</t>
+          <t>RAM SINGH SHUKLA</t>
         </is>
       </c>
       <c r="C570" t="inlineStr">
         <is>
-          <t>IND</t>
+          <t>BMUP</t>
         </is>
       </c>
       <c r="D570" t="n">
-        <v>16536</v>
+        <v>16544</v>
       </c>
       <c r="E570" t="n">
         <v>18</v>
@@ -35784,12 +35784,12 @@
       </c>
       <c r="K570" t="inlineStr">
         <is>
-          <t>ASHOK SHARMA</t>
+          <t>RAM SINGH SHUKLA</t>
         </is>
       </c>
       <c r="L570" t="inlineStr">
         <is>
-          <t>IND</t>
+          <t>BMUP</t>
         </is>
       </c>
       <c r="Q570" t="b">
@@ -49644,11 +49644,11 @@
       </c>
       <c r="C794" t="inlineStr">
         <is>
-          <t>CPM</t>
+          <t>CPI(M)</t>
         </is>
       </c>
       <c r="D794" t="n">
-        <v>16552</v>
+        <v>26432</v>
       </c>
       <c r="E794" t="n">
         <v>3273</v>
@@ -51256,11 +51256,11 @@
       </c>
       <c r="C820" t="inlineStr">
         <is>
-          <t>CPM</t>
+          <t>CPI(M)</t>
         </is>
       </c>
       <c r="D820" t="n">
-        <v>16552</v>
+        <v>26432</v>
       </c>
       <c r="E820" t="n">
         <v>610</v>
